--- a/output/detection/gender_gap.xlsx
+++ b/output/detection/gender_gap.xlsx
@@ -436,7 +436,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Grade</t>
+          <t>Niveau</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
